--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCFA039-CF9A-40F5-89AD-A4C546D98BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A8AE0D-643F-4019-87E5-0F0A7E70B127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -431,7 +431,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1756,136 +1768,280 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+      <c r="A22" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>130</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>100</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" ref="I22:I27" si="2">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <v>970</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" ref="J22:J27" si="3">IF(I22="","",1440-I22)</f>
+        <v>470</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+      <c r="A23" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>100</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="2"/>
+        <v>1060</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" si="3"/>
+        <v>380</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+      <c r="A24" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>100</v>
+      </c>
+      <c r="E24" s="14">
+        <v>130</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>100</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="2"/>
+        <v>890</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+      <c r="A25" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>180</v>
+      </c>
+      <c r="E25" s="14">
+        <v>170</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>100</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="A26" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>100</v>
+      </c>
+      <c r="E26" s="14">
+        <v>150</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>100</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="2"/>
+        <v>710</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="3"/>
+        <v>730</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+      <c r="A27" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>100</v>
+      </c>
+      <c r="E27" s="14">
+        <v>130</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>100</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="2"/>
+        <v>890</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
@@ -2821,11 +2977,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2843,11 +2999,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2865,11 +3021,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2887,11 +3043,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2909,11 +3065,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2931,11 +3087,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2953,11 +3109,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2975,11 +3131,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2997,11 +3153,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3019,11 +3175,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3041,11 +3197,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3063,11 +3219,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3085,11 +3241,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3107,11 +3263,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3129,11 +3285,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3151,11 +3307,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3173,11 +3329,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3195,11 +3351,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3217,11 +3373,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3239,11 +3395,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3261,11 +3417,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3283,11 +3439,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3305,11 +3461,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3327,11 +3483,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3349,11 +3505,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3371,11 +3527,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3393,11 +3549,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3415,11 +3571,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3437,11 +3593,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3459,11 +3615,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3481,11 +3637,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3503,11 +3659,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3525,11 +3681,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3547,11 +3703,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3569,11 +3725,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3591,11 +3747,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3613,11 +3769,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3635,11 +3791,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3657,11 +3813,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3679,11 +3835,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3701,11 +3857,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3723,11 +3879,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3745,11 +3901,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3767,11 +3923,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3789,11 +3945,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3811,11 +3967,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3833,11 +3989,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3855,11 +4011,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3877,11 +4033,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3899,11 +4055,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3921,11 +4077,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3943,11 +4099,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3965,11 +4121,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3987,11 +4143,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4009,11 +4165,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4031,11 +4187,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4053,11 +4209,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4075,11 +4231,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4097,11 +4253,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4119,11 +4275,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4141,11 +4297,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4163,11 +4319,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4185,11 +4341,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4207,11 +4363,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4229,11 +4385,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4251,11 +4407,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4273,11 +4429,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4295,11 +4451,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4317,11 +4473,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4339,11 +4495,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4361,11 +4517,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4383,11 +4539,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4405,11 +4561,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4427,11 +4583,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4449,11 +4605,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4471,11 +4627,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4493,11 +4649,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4515,11 +4671,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4537,11 +4693,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4559,11 +4715,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4581,11 +4737,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4603,11 +4759,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4625,11 +4781,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4647,11 +4803,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4669,11 +4825,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4691,11 +4847,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4713,11 +4869,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4735,11 +4891,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4757,11 +4913,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4779,11 +4935,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4801,11 +4957,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4823,11 +4979,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4845,11 +5001,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4867,11 +5023,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4889,11 +5045,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4911,11 +5067,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4933,11 +5089,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4955,11 +5111,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4977,11 +5133,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4999,11 +5155,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5021,11 +5177,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5043,11 +5199,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5065,11 +5221,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5087,11 +5243,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5109,11 +5265,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5131,11 +5287,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5153,11 +5309,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5175,11 +5331,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5197,11 +5353,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5219,11 +5375,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5241,11 +5397,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5263,11 +5419,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5285,11 +5441,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5307,11 +5463,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5329,11 +5485,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5351,11 +5507,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5373,11 +5529,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5395,11 +5551,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5417,11 +5573,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5439,11 +5595,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5461,11 +5617,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5483,11 +5639,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5505,11 +5661,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5527,11 +5683,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5549,11 +5705,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5571,11 +5727,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5593,11 +5749,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5615,11 +5771,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5637,11 +5793,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5659,11 +5815,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5681,11 +5837,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5703,11 +5859,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5725,11 +5881,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5747,11 +5903,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5769,11 +5925,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5791,11 +5947,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5813,11 +5969,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5835,11 +5991,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5857,11 +6013,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5879,11 +6035,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5901,11 +6057,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5923,11 +6079,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5945,11 +6101,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5967,11 +6123,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5989,11 +6145,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6011,11 +6167,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6033,11 +6189,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6055,11 +6211,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6077,11 +6233,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6099,11 +6255,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6121,11 +6277,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6143,11 +6299,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6165,11 +6321,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6187,11 +6343,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6209,11 +6365,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6231,11 +6387,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6253,11 +6409,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6275,11 +6431,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6297,11 +6453,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6319,11 +6475,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6341,11 +6497,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6363,11 +6519,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6385,11 +6541,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6407,11 +6563,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6429,11 +6585,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6451,11 +6607,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6473,11 +6629,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6495,11 +6651,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6517,11 +6673,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6539,11 +6695,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6561,11 +6717,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6583,11 +6739,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6605,11 +6761,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6627,11 +6783,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6649,11 +6805,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6671,11 +6827,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6693,11 +6849,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6715,11 +6871,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6737,11 +6893,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6759,11 +6915,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6781,11 +6937,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6803,11 +6959,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6825,11 +6981,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6847,11 +7003,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6869,11 +7025,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6891,11 +7047,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6913,11 +7069,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6935,11 +7091,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6957,11 +7113,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6979,11 +7135,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7001,11 +7157,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7023,11 +7179,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7045,11 +7201,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7067,11 +7223,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7089,11 +7245,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7111,11 +7267,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7133,11 +7289,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7155,11 +7311,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7177,11 +7333,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7199,11 +7355,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7221,11 +7377,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7243,11 +7399,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7265,11 +7421,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7287,11 +7443,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7309,11 +7465,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7331,11 +7487,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7353,11 +7509,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7375,11 +7531,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7397,11 +7553,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7419,11 +7575,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7441,11 +7597,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7463,11 +7619,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7485,11 +7641,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7507,11 +7663,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7529,11 +7685,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7551,11 +7707,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7573,11 +7729,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7595,11 +7751,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7617,11 +7773,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7639,11 +7795,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7661,11 +7817,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7683,11 +7839,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7705,11 +7861,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7727,11 +7883,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7749,11 +7905,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7771,11 +7927,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7793,11 +7949,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7815,11 +7971,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7837,11 +7993,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7859,11 +8015,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7881,11 +8037,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7903,11 +8059,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7925,11 +8081,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7947,11 +8103,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7969,11 +8125,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7991,11 +8147,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8013,11 +8169,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8035,11 +8191,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8057,11 +8213,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8079,11 +8235,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8101,11 +8257,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8123,11 +8279,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8145,11 +8301,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8167,11 +8323,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8189,11 +8345,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8211,11 +8367,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8233,11 +8389,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8255,11 +8411,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8277,11 +8433,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8299,11 +8455,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8321,11 +8477,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8343,11 +8499,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8365,11 +8521,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8387,11 +8543,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8409,11 +8565,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8431,11 +8587,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8453,11 +8609,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8475,11 +8631,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8497,11 +8653,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8519,11 +8675,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8541,11 +8697,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8563,11 +8719,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8585,11 +8741,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8607,11 +8763,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8629,11 +8785,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8651,11 +8807,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8673,11 +8829,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8695,11 +8851,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8717,11 +8873,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8739,11 +8895,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8761,11 +8917,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8783,11 +8939,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8805,11 +8961,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8827,11 +8983,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8849,11 +9005,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8871,11 +9027,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8893,11 +9049,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8915,11 +9071,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8937,11 +9093,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8959,11 +9115,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8981,11 +9137,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9003,11 +9159,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9025,11 +9181,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9047,11 +9203,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9069,11 +9225,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9091,11 +9247,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9113,11 +9269,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9135,11 +9291,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9157,11 +9313,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9179,11 +9335,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9201,11 +9357,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9223,11 +9379,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9245,11 +9401,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9267,11 +9423,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9289,11 +9445,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9311,11 +9467,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9333,11 +9489,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9355,11 +9511,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9377,11 +9533,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9399,11 +9555,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9421,11 +9577,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9443,11 +9599,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9465,11 +9621,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9487,11 +9643,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9509,11 +9665,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9531,11 +9687,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9553,11 +9709,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9575,11 +9731,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9597,11 +9753,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9619,11 +9775,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9641,11 +9797,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9663,11 +9819,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9685,11 +9841,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9707,11 +9863,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9729,11 +9885,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9751,11 +9907,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9773,11 +9929,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9795,11 +9951,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9817,11 +9973,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9839,11 +9995,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9861,11 +10017,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9883,11 +10039,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9905,11 +10061,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9927,11 +10083,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9949,11 +10105,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9971,11 +10127,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9993,11 +10149,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10015,11 +10171,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10037,11 +10193,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10059,11 +10215,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10081,11 +10237,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10103,11 +10259,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -10125,7 +10281,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A8AE0D-643F-4019-87E5-0F0A7E70B127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1805D5E9-0281-4D70-B262-BAA93046EF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -246,6 +246,9 @@
   <si>
     <t>Preparing for CA</t>
   </si>
+  <si>
+    <t>It was hectic day</t>
+  </si>
 </sst>
 </file>
 
@@ -431,19 +434,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2044,26 +2035,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B28" s="14">
+        <v>400</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>120</v>
+      </c>
+      <c r="F28" s="14">
+        <v>250</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>90</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
@@ -10281,7 +10296,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1805D5E9-0281-4D70-B262-BAA93046EF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D85345-3258-4748-BF43-01307712567A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>It was hectic day</t>
+  </si>
+  <si>
+    <t>CA Prepartion day</t>
   </si>
 </sst>
 </file>
@@ -2081,48 +2084,96 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>70</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>160</v>
+      </c>
+      <c r="E30" s="14">
+        <v>40</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14">
+        <v>90</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D85345-3258-4748-BF43-01307712567A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575D9755-6BDA-40EF-A9A0-132C963E6E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2176,26 +2176,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B31" s="14">
+        <v>250</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>350</v>
+      </c>
+      <c r="G31" s="14">
+        <v>7</v>
+      </c>
+      <c r="H31" s="14">
+        <v>100</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hiii\Desktop\12602516\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575D9755-6BDA-40EF-A9A0-132C963E6E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664679A2-31DD-487D-A93A-0DE0F2DBBDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,24 @@
   </si>
   <si>
     <t>CA Prepartion day</t>
+  </si>
+  <si>
+    <t>It was good day as there is no class</t>
+  </si>
+  <si>
+    <t>Worked for project</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Laptop was not working ssd issue</t>
+  </si>
+  <si>
+    <t>Given for laptop repairing</t>
   </si>
 </sst>
 </file>
@@ -2221,115 +2239,235 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B32" s="14">
+        <v>400</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>200</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B33" s="14">
+        <v>380</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>200</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>100</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B34" s="14">
+        <v>400</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>90</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>90</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B35" s="14">
+        <v>360</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="14">
+        <v>400</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hiii\Desktop\12602516\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAD5FE4-24E5-4371-BCDA-6267876245A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB76381-9BAE-43B7-A927-E6287D77EF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,171 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="86">
+  <si>
+    <t>My Data, My Code — Daily Log</t>
+  </si>
+  <si>
+    <t>Name:</t>
+  </si>
+  <si>
+    <t>Himanshu Gupta</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
+  </si>
+  <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
+    <t>CAP-776</t>
+  </si>
+  <si>
+    <t>Month:</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Sleep (min)</t>
+  </si>
+  <si>
+    <t>Fitness (min)</t>
+  </si>
+  <si>
+    <t>Study (min)</t>
+  </si>
+  <si>
+    <t>Coding (min)</t>
+  </si>
+  <si>
+    <t>Class (min)</t>
+  </si>
+  <si>
+    <t>Classes Attended</t>
+  </si>
+  <si>
+    <t>Other Activities (min)</t>
+  </si>
+  <si>
+    <t>Total Tracked (min)</t>
+  </si>
+  <si>
+    <t>Free/Unaccounted (min)</t>
+  </si>
+  <si>
+    <t>Day's Feeling</t>
+  </si>
+  <si>
+    <t>Satisfaction Level</t>
+  </si>
+  <si>
+    <t>Energy Level</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Educational day</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>It was busy day</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Worked for project</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Project working day</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Good Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was good day </t>
+  </si>
+  <si>
+    <t>Tired day</t>
+  </si>
+  <si>
+    <t>Hectic Day</t>
+  </si>
+  <si>
+    <t>Working day</t>
+  </si>
+  <si>
+    <t>Preparing for CA</t>
+  </si>
+  <si>
+    <t>It was hectic day</t>
+  </si>
+  <si>
+    <t>CA Prepartion day</t>
+  </si>
+  <si>
+    <t>It was good day as there is no class</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Laptop was not working ssd issue</t>
+  </si>
+  <si>
+    <t>Given for laptop repairing</t>
+  </si>
+  <si>
+    <t>Got laptop back from repair and attended classes</t>
+  </si>
+  <si>
+    <t>Weekend self-study and project coding</t>
+  </si>
+  <si>
+    <t>Sunday revision and minor project documentation</t>
+  </si>
+  <si>
+    <t>Project testing and code optimization</t>
+  </si>
+  <si>
+    <t>Final project review and activity log update</t>
+  </si>
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -118,157 +274,22 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
-    <t>My Data, My Code — Daily Log</t>
+    <t>Attended classes</t>
   </si>
   <si>
-    <t>Name:</t>
+    <t>self-study, no regular classes</t>
   </si>
   <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
-    <t>Course / Section:</t>
-  </si>
-  <si>
-    <t>Month:</t>
-  </si>
-  <si>
-    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Sleep (min)</t>
-  </si>
-  <si>
-    <t>Fitness (min)</t>
-  </si>
-  <si>
-    <t>Study (min)</t>
-  </si>
-  <si>
-    <t>Coding (min)</t>
-  </si>
-  <si>
-    <t>Class (min)</t>
-  </si>
-  <si>
-    <t>Classes Attended</t>
-  </si>
-  <si>
-    <t>Other Activities (min)</t>
-  </si>
-  <si>
-    <t>Total Tracked (min)</t>
-  </si>
-  <si>
-    <t>Free/Unaccounted (min)</t>
-  </si>
-  <si>
-    <t>Day's Feeling</t>
-  </si>
-  <si>
-    <t>Satisfaction Level</t>
-  </si>
-  <si>
-    <t>Energy Level</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Good</t>
-  </si>
-  <si>
-    <t>Satisfied</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>5. GOOD PRACTICE</t>
-  </si>
-  <si>
-    <t>Educational day</t>
-  </si>
-  <si>
-    <t>Himanshu Gupta</t>
-  </si>
-  <si>
-    <t>CAP-776</t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
-    <t>Excellent</t>
-  </si>
-  <si>
-    <t>Very Satisfied</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Good Day</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>Hectic Day</t>
-  </si>
-  <si>
-    <t>Project working day</t>
-  </si>
-  <si>
-    <t>Working day</t>
-  </si>
-  <si>
-    <t>Tired day</t>
-  </si>
-  <si>
-    <t>It was busy day</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Preparing for CA</t>
-  </si>
-  <si>
-    <t>It was hectic day</t>
-  </si>
-  <si>
-    <t>CA Prepartion day</t>
-  </si>
-  <si>
-    <t>It was good day as there is no class</t>
-  </si>
-  <si>
-    <t>Worked for project</t>
-  </si>
-  <si>
-    <t>Stressed</t>
-  </si>
-  <si>
-    <t>Unsatisfied</t>
-  </si>
-  <si>
-    <t>Laptop was not working ssd issue</t>
-  </si>
-  <si>
-    <t>Given for laptop repairing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It was good day </t>
+    <t>project implementation</t>
   </si>
 </sst>
 </file>
@@ -373,7 +394,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -396,11 +417,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -426,9 +471,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,19 +760,19 @@
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="22.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
@@ -732,12 +780,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
@@ -745,22 +793,22 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
@@ -768,17 +816,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
@@ -786,77 +834,77 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
@@ -864,17 +912,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
@@ -912,117 +960,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
       </c>
       <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="15">
+        <v>3</v>
+      </c>
+      <c r="F2" s="13">
         <v>12602516</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>5</v>
       </c>
       <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="D3" s="14"/>
       <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="15"/>
+        <v>6</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-    </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+    </row>
+    <row r="5" spans="1:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1051,24 +1099,24 @@
         <v>180</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I74" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1190</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J74" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
         <v>250</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1097,24 +1145,24 @@
         <v>100</v>
       </c>
       <c r="I7" s="10">
-        <f t="shared" ref="I7:I12" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J7" s="10">
-        <f t="shared" ref="J7:J12" si="3">IF(I7="","",1440-I7)</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1143,24 +1191,24 @@
         <v>100</v>
       </c>
       <c r="I8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1090</v>
       </c>
       <c r="J8" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>350</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1189,24 +1237,24 @@
         <v>180</v>
       </c>
       <c r="I9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1260</v>
       </c>
       <c r="J9" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1235,24 +1283,24 @@
         <v>120</v>
       </c>
       <c r="I10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>950</v>
       </c>
       <c r="J10" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>490</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1281,24 +1329,24 @@
         <v>120</v>
       </c>
       <c r="I11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>580</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1327,24 +1375,24 @@
         <v>100</v>
       </c>
       <c r="I12" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>900</v>
       </c>
       <c r="J12" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>540</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1381,16 +1429,16 @@
         <v>360</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1427,16 +1475,16 @@
         <v>380</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1473,16 +1521,16 @@
         <v>450</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1519,16 +1567,16 @@
         <v>150</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1565,16 +1613,16 @@
         <v>460</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1611,16 +1659,16 @@
         <v>540</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1657,16 +1705,16 @@
         <v>360</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1703,16 +1751,16 @@
         <v>350</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1749,16 +1797,16 @@
         <v>440</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1795,16 +1843,16 @@
         <v>400</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1841,16 +1889,16 @@
         <v>710</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1887,16 +1935,16 @@
         <v>670</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1933,16 +1981,16 @@
         <v>600</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1979,16 +2027,16 @@
         <v>550</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2017,24 +2065,24 @@
         <v>100</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" ref="I27:I32" si="4">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <f t="shared" si="0"/>
         <v>970</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" ref="J27:J32" si="5">IF(I27="","",1440-I27)</f>
+        <f t="shared" si="1"/>
         <v>470</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2063,24 +2111,24 @@
         <v>100</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>1060</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>380</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2109,24 +2157,24 @@
         <v>100</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>550</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2155,24 +2203,24 @@
         <v>100</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>810</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>630</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2201,24 +2249,24 @@
         <v>100</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>710</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>730</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2247,24 +2295,24 @@
         <v>100</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>550</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2301,16 +2349,16 @@
         <v>400</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2347,16 +2395,16 @@
         <v>380</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2393,16 +2441,16 @@
         <v>370</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2439,19 +2487,19 @@
         <v>530</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46284</v>
       </c>
@@ -2485,16 +2533,16 @@
         <v>660</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2531,19 +2579,19 @@
         <v>380</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46286</v>
       </c>
@@ -2577,16 +2625,16 @@
         <v>430</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2623,16 +2671,16 @@
         <v>510</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2669,193 +2717,385 @@
         <v>380</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="L41" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B42" s="9">
+        <v>420</v>
+      </c>
+      <c r="C42" s="9">
+        <v>60</v>
+      </c>
+      <c r="D42" s="9">
+        <v>150</v>
+      </c>
+      <c r="E42" s="9">
+        <v>90</v>
+      </c>
+      <c r="F42" s="9">
+        <v>250</v>
+      </c>
+      <c r="G42" s="9">
+        <v>5</v>
+      </c>
+      <c r="H42" s="9">
+        <v>100</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="0"/>
+        <v>1070</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B43" s="9">
+        <v>400</v>
+      </c>
+      <c r="C43" s="9">
+        <v>60</v>
+      </c>
+      <c r="D43" s="9">
+        <v>180</v>
+      </c>
+      <c r="E43" s="9">
+        <v>100</v>
+      </c>
+      <c r="F43" s="9">
+        <v>200</v>
+      </c>
+      <c r="G43" s="9">
+        <v>4</v>
+      </c>
+      <c r="H43" s="9">
+        <v>90</v>
+      </c>
+      <c r="I43" s="10">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J43" s="10">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B44" s="9">
+        <v>480</v>
+      </c>
+      <c r="C44" s="9">
+        <v>60</v>
+      </c>
+      <c r="D44" s="9">
+        <v>240</v>
+      </c>
+      <c r="E44" s="9">
+        <v>180</v>
+      </c>
+      <c r="F44" s="9">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>120</v>
+      </c>
+      <c r="I44" s="10">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J44" s="10">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B45" s="9">
+        <v>480</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0</v>
+      </c>
+      <c r="D45" s="9">
+        <v>260</v>
+      </c>
+      <c r="E45" s="9">
+        <v>150</v>
+      </c>
+      <c r="F45" s="9">
+        <v>0</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9">
+        <v>120</v>
+      </c>
+      <c r="I45" s="10">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N45" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="M41" s="11" t="s">
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B46" s="9">
+        <v>420</v>
+      </c>
+      <c r="C46" s="9">
+        <v>60</v>
+      </c>
+      <c r="D46" s="9">
+        <v>280</v>
+      </c>
+      <c r="E46" s="9">
+        <v>120</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>110</v>
+      </c>
+      <c r="I46" s="10">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J46" s="10">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B47" s="9">
+        <v>400</v>
+      </c>
+      <c r="C47" s="9">
+        <v>60</v>
+      </c>
+      <c r="D47" s="9">
+        <v>270</v>
+      </c>
+      <c r="E47" s="9">
+        <v>140</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>120</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J47" s="10">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B48" s="9">
+        <v>420</v>
+      </c>
+      <c r="C48" s="9">
+        <v>60</v>
+      </c>
+      <c r="D48" s="9">
+        <v>240</v>
+      </c>
+      <c r="E48" s="9">
+        <v>160</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>120</v>
+      </c>
+      <c r="I48" s="10">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J48" s="10">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N48" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="N41" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
+    </row>
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B49" s="9">
+        <v>420</v>
+      </c>
+      <c r="C49" s="9">
+        <v>60</v>
+      </c>
+      <c r="D49" s="9">
+        <v>220</v>
+      </c>
+      <c r="E49" s="9">
+        <v>150</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>130</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
+        <v>460</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
@@ -3307,11 +3547,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3329,11 +3569,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3351,11 +3591,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3373,11 +3613,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3395,11 +3635,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3417,11 +3657,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" ref="I75:I138" si="6">IF(SUM(B75:F75,H75)=0,"",SUM(B75:F75,H75))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" ref="J75:J138" si="7">IF(I75="","",1440-I75)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3439,11 +3679,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3461,11 +3701,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3483,11 +3723,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3505,11 +3745,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3527,11 +3767,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3549,11 +3789,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3571,11 +3811,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3593,11 +3833,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3615,11 +3855,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3637,11 +3877,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3659,11 +3899,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3681,11 +3921,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3703,11 +3943,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3725,11 +3965,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3747,11 +3987,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3769,11 +4009,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3791,11 +4031,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3813,11 +4053,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3835,11 +4075,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3857,11 +4097,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3879,11 +4119,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3901,11 +4141,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3923,11 +4163,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3945,11 +4185,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3967,11 +4207,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3989,11 +4229,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4011,11 +4251,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4033,11 +4273,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4055,11 +4295,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4077,11 +4317,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4099,11 +4339,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4121,11 +4361,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4143,11 +4383,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4165,11 +4405,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4187,11 +4427,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4209,11 +4449,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4231,11 +4471,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4253,11 +4493,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4275,11 +4515,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4297,11 +4537,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4319,11 +4559,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4341,11 +4581,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4363,11 +4603,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4385,11 +4625,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4407,11 +4647,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4429,11 +4669,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4451,11 +4691,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4473,11 +4713,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4495,11 +4735,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4517,11 +4757,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4539,11 +4779,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4561,11 +4801,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4583,11 +4823,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4605,11 +4845,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4627,11 +4867,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4649,11 +4889,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4671,11 +4911,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4693,11 +4933,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4715,11 +4955,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4737,11 +4977,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4759,11 +4999,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4781,11 +5021,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4803,11 +5043,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4825,11 +5065,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" ref="I139:I202" si="8">IF(SUM(B139:F139,H139)=0,"",SUM(B139:F139,H139))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" ref="J139:J202" si="9">IF(I139="","",1440-I139)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4847,11 +5087,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4869,11 +5109,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4891,11 +5131,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4913,11 +5153,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4935,11 +5175,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4957,11 +5197,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4979,11 +5219,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5001,11 +5241,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5023,11 +5263,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5045,11 +5285,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5067,11 +5307,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5089,11 +5329,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5111,11 +5351,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5133,11 +5373,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5155,11 +5395,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5177,11 +5417,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5199,11 +5439,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5221,11 +5461,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5243,11 +5483,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5265,11 +5505,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5287,11 +5527,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5309,11 +5549,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5331,11 +5571,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5353,11 +5593,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5375,11 +5615,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5397,11 +5637,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5419,11 +5659,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5441,11 +5681,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5463,11 +5703,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5485,11 +5725,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5507,11 +5747,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5529,11 +5769,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5551,11 +5791,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5573,11 +5813,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5595,11 +5835,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5617,11 +5857,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5639,11 +5879,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5661,11 +5901,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5683,11 +5923,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5705,11 +5945,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5727,11 +5967,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5749,11 +5989,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5771,11 +6011,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5793,11 +6033,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5815,11 +6055,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5837,11 +6077,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5859,11 +6099,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5881,11 +6121,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5903,11 +6143,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5925,11 +6165,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5947,11 +6187,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5969,11 +6209,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5991,11 +6231,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6013,11 +6253,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6035,11 +6275,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6057,11 +6297,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6079,11 +6319,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6101,11 +6341,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6123,11 +6363,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6145,11 +6385,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6167,11 +6407,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6189,11 +6429,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6211,11 +6451,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6233,11 +6473,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" ref="I203:I266" si="10">IF(SUM(B203:F203,H203)=0,"",SUM(B203:F203,H203))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" ref="J203:J266" si="11">IF(I203="","",1440-I203)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6255,11 +6495,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6277,11 +6517,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6299,11 +6539,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6321,11 +6561,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6343,11 +6583,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6365,11 +6605,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6387,11 +6627,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6409,11 +6649,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6431,11 +6671,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6453,11 +6693,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6475,11 +6715,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6497,11 +6737,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6519,11 +6759,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6541,11 +6781,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6563,11 +6803,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6585,11 +6825,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6607,11 +6847,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6629,11 +6869,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6651,11 +6891,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6673,11 +6913,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6695,11 +6935,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6717,11 +6957,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6739,11 +6979,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6761,11 +7001,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6783,11 +7023,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6805,11 +7045,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6827,11 +7067,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6849,11 +7089,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6871,11 +7111,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6893,11 +7133,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6915,11 +7155,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6937,11 +7177,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6959,11 +7199,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6981,11 +7221,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7003,11 +7243,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7025,11 +7265,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7047,11 +7287,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7069,11 +7309,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7091,11 +7331,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7113,11 +7353,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7135,11 +7375,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7157,11 +7397,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7179,11 +7419,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7201,11 +7441,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7223,11 +7463,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7245,11 +7485,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7267,11 +7507,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7289,11 +7529,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7311,11 +7551,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7333,11 +7573,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7355,11 +7595,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7377,11 +7617,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7399,11 +7639,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7421,11 +7661,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7443,11 +7683,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7465,11 +7705,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7487,11 +7727,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7509,11 +7749,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7531,11 +7771,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7553,11 +7793,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7575,11 +7815,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7597,11 +7837,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7619,11 +7859,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7641,11 +7881,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" ref="I267:I330" si="12">IF(SUM(B267:F267,H267)=0,"",SUM(B267:F267,H267))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" ref="J267:J330" si="13">IF(I267="","",1440-I267)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7663,11 +7903,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7685,11 +7925,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7707,11 +7947,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7729,11 +7969,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7751,11 +7991,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7773,11 +8013,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7795,11 +8035,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7817,11 +8057,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7839,11 +8079,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7861,11 +8101,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7883,11 +8123,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7905,11 +8145,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7927,11 +8167,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7949,11 +8189,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7971,11 +8211,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7993,11 +8233,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8015,11 +8255,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8037,11 +8277,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8059,11 +8299,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8081,11 +8321,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8103,11 +8343,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8125,11 +8365,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8147,11 +8387,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8169,11 +8409,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8191,11 +8431,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8213,11 +8453,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8235,11 +8475,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8257,11 +8497,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8279,11 +8519,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8301,11 +8541,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8323,11 +8563,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8345,11 +8585,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8367,11 +8607,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8389,11 +8629,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8411,11 +8651,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8433,11 +8673,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8455,11 +8695,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8477,11 +8717,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8499,11 +8739,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8521,11 +8761,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8543,11 +8783,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8565,11 +8805,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8587,11 +8827,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8609,11 +8849,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8631,11 +8871,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8653,11 +8893,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8675,11 +8915,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8697,11 +8937,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8719,11 +8959,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8741,11 +8981,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8763,11 +9003,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8785,11 +9025,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8807,11 +9047,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8829,11 +9069,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8851,11 +9091,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8873,11 +9113,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8895,11 +9135,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8917,11 +9157,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8939,11 +9179,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8961,11 +9201,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8983,11 +9223,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9005,11 +9245,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9027,11 +9267,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9049,11 +9289,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" ref="I331:I394" si="14">IF(SUM(B331:F331,H331)=0,"",SUM(B331:F331,H331))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" ref="J331:J394" si="15">IF(I331="","",1440-I331)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9071,11 +9311,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9093,11 +9333,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9115,11 +9355,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9137,11 +9377,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9159,11 +9399,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9181,11 +9421,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9203,11 +9443,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9225,11 +9465,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9247,11 +9487,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9269,11 +9509,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9291,11 +9531,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9313,11 +9553,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9335,11 +9575,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9357,11 +9597,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9379,11 +9619,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9401,11 +9641,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9423,11 +9663,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9445,11 +9685,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9467,11 +9707,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9489,11 +9729,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9511,11 +9751,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9533,11 +9773,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9555,11 +9795,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9577,11 +9817,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9599,11 +9839,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9621,11 +9861,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9643,11 +9883,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9665,11 +9905,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9687,11 +9927,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9709,11 +9949,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9731,11 +9971,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9753,11 +9993,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9775,11 +10015,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9797,11 +10037,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9819,11 +10059,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9841,11 +10081,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9863,11 +10103,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9885,11 +10125,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9907,11 +10147,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9929,11 +10169,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9951,11 +10191,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9973,11 +10213,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9995,11 +10235,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10017,11 +10257,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10039,11 +10279,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10061,11 +10301,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10083,11 +10323,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10105,11 +10345,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10127,11 +10367,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10149,11 +10389,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10171,11 +10411,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10193,11 +10433,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10215,11 +10455,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10237,11 +10477,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10259,11 +10499,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10281,11 +10521,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10303,11 +10543,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10325,11 +10565,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10347,11 +10587,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I390:I453" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="J390:J453" si="13">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10369,11 +10609,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10391,11 +10631,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10413,11 +10653,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10435,11 +10675,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10457,11 +10697,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" ref="I395:I406" si="16">IF(SUM(B395:F395,H395)=0,"",SUM(B395:F395,H395))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" ref="J395:J406" si="17">IF(I395="","",1440-I395)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10479,11 +10719,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10501,11 +10741,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10523,11 +10763,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10545,11 +10785,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10567,11 +10807,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10589,11 +10829,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K401" s="11"/>
@@ -10611,11 +10851,11 @@
       <c r="G402" s="9"/>
       <c r="H402" s="9"/>
       <c r="I402" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J402" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K402" s="11"/>
@@ -10633,11 +10873,11 @@
       <c r="G403" s="9"/>
       <c r="H403" s="9"/>
       <c r="I403" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J403" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K403" s="11"/>
@@ -10655,11 +10895,11 @@
       <c r="G404" s="9"/>
       <c r="H404" s="9"/>
       <c r="I404" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J404" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K404" s="11"/>
@@ -10677,11 +10917,11 @@
       <c r="G405" s="9"/>
       <c r="H405" s="9"/>
       <c r="I405" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J405" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K405" s="11"/>
@@ -10699,11 +10939,11 @@
       <c r="G406" s="9"/>
       <c r="H406" s="9"/>
       <c r="I406" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J406" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K406" s="11"/>
@@ -10713,12 +10953,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A4:N4"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J406">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
